--- a/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26914"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,14 +10,14 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67715FF-ECB8-403C-85D4-482D3A4407C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="825" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="825" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="EIA Table 1" sheetId="2" r:id="rId2"/>
     <sheet name="EoCEDwEC" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,12 +46,93 @@
     <t>U.S. Energy Information Administration</t>
   </si>
   <si>
+    <t>Price Elasticities for Energy Use in Buildings of the United States</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/analysis/studies/buildings/energyuse/pdf/price_elasticities.pdf</t>
+  </si>
+  <si>
+    <t>page 3: Table 1, Table 2</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>We use same-price, long-run elasticities minus the 3-year short-run elasticities.</t>
+  </si>
+  <si>
+    <t>We calculate it this way because we assume that 3-year elasticities primarily reflect behavior</t>
+  </si>
+  <si>
+    <t>change rather than equipment change, and the response of behavior to price per unit service</t>
+  </si>
+  <si>
+    <t>provided (that is, controlling for things like efficiency of equipment) should be constant at</t>
+  </si>
+  <si>
+    <t>all timescales.  So, the portion of the long-run elasticitiy represented by the 3-year elasticity</t>
+  </si>
+  <si>
+    <t>is still behavior change, and the rest is equipment efficiency change, which is what we are</t>
+  </si>
+  <si>
+    <t>looking for here.  (The non-behavior long-run elasticity should be fully implemented in the</t>
+  </si>
+  <si>
+    <t>current model year, and its effects gradually filter into the fleet of building components as</t>
+  </si>
+  <si>
+    <t>new components are deployed and old ones are retired.)</t>
+  </si>
+  <si>
+    <t>Note that the source doesn't provide coal or district heat.  We assume the elasticity of</t>
+  </si>
+  <si>
+    <t>coal heating equipment efficiency is similar to that of petroleum heating equipment.</t>
+  </si>
+  <si>
+    <t>We assume the efficiency of district heating equipment is not under the control of the</t>
+  </si>
+  <si>
+    <t>building owners or operators, and changes in efficiency of this equipment are handled</t>
+  </si>
+  <si>
+    <t>in the District Heating module.</t>
+  </si>
+  <si>
+    <t>We assume that biomass (wood) used in buildings is harvested by building users and</t>
+  </si>
+  <si>
+    <t>therefore wood consumption is inelastic with respect to the price of wood in stores.</t>
+  </si>
+  <si>
+    <t>We assume kerosene and fuel oil-burning equipment is similar to diesel-burning equipment.</t>
+  </si>
+  <si>
+    <t>We assume LPG/propane/butane-burning equipment is similar to natural gas-burning equipment.</t>
+  </si>
+  <si>
+    <t>We assume hydrogen-using equipment is similar to electricity-using equipment (as it may</t>
+  </si>
+  <si>
+    <t>contain fuel cells that produce electricity from hydrogen).</t>
+  </si>
+  <si>
+    <t>This is a subset of Table 1 that includes only values from AEO2020 (not AEO99).</t>
+  </si>
+  <si>
     <t>It includes only the "Residential" and "Commercial" sections.</t>
   </si>
   <si>
     <t>Residential</t>
   </si>
   <si>
+    <t>Short-Run Own-Price Elasticity</t>
+  </si>
+  <si>
+    <t>Long-Run Own-Price and Cross-Price Elasticity</t>
+  </si>
+  <si>
     <t>Fuel</t>
   </si>
   <si>
@@ -72,15 +154,21 @@
     <t>Distillate Fuel</t>
   </si>
   <si>
-    <t>Short-Run Own-Price Elasticity</t>
-  </si>
-  <si>
-    <t>Long-Run Own-Price and Cross-Price Elasticity</t>
-  </si>
-  <si>
     <t>Commercial</t>
   </si>
   <si>
+    <t xml:space="preserve">**Note from April 2023 - there has not been an updated version of this report. This is the most recent own-price elasticity data </t>
+  </si>
+  <si>
+    <t>Elasticity by Fuel (dimensionless)</t>
+  </si>
+  <si>
+    <t>Urban Residential</t>
+  </si>
+  <si>
+    <t>Rural Residential</t>
+  </si>
+  <si>
     <t>electricity</t>
   </si>
   <si>
@@ -96,57 +184,9 @@
     <t>heat</t>
   </si>
   <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t>change rather than equipment change, and the response of behavior to price per unit service</t>
-  </si>
-  <si>
-    <t>provided (that is, controlling for things like efficiency of equipment) should be constant at</t>
-  </si>
-  <si>
-    <t>is still behavior change, and the rest is equipment efficiency change, which is what we are</t>
-  </si>
-  <si>
-    <t>looking for here.  (The non-behavior long-run elasticity should be fully implemented in the</t>
-  </si>
-  <si>
-    <t>current model year, and its effects gradually filter into the fleet of building components as</t>
-  </si>
-  <si>
-    <t>new components are deployed and old ones are retired.)</t>
-  </si>
-  <si>
-    <t>Note that the source doesn't provide coal or district heat.  We assume the elasticity of</t>
-  </si>
-  <si>
-    <t>coal heating equipment efficiency is similar to that of petroleum heating equipment.</t>
-  </si>
-  <si>
-    <t>We assume the efficiency of district heating equipment is not under the control of the</t>
-  </si>
-  <si>
-    <t>building owners or operators, and changes in efficiency of this equipment are handled</t>
-  </si>
-  <si>
-    <t>in the District Heating module.</t>
-  </si>
-  <si>
-    <t>Urban Residential</t>
-  </si>
-  <si>
-    <t>Rural Residential</t>
-  </si>
-  <si>
     <t>biomass</t>
   </si>
   <si>
-    <t>We assume that biomass (wood) used in buildings is harvested by building users and</t>
-  </si>
-  <si>
-    <t>therefore wood consumption is inelastic with respect to the price of wood in stores.</t>
-  </si>
-  <si>
     <t>kerosene</t>
   </si>
   <si>
@@ -157,52 +197,13 @@
   </si>
   <si>
     <t>hydrogen</t>
-  </si>
-  <si>
-    <t>We assume kerosene and fuel oil-burning equipment is similar to diesel-burning equipment.</t>
-  </si>
-  <si>
-    <t>We assume LPG/propane/butane-burning equipment is similar to natural gas-burning equipment.</t>
-  </si>
-  <si>
-    <t>We assume hydrogen-using equipment is similar to electricity-using equipment (as it may</t>
-  </si>
-  <si>
-    <t>contain fuel cells that produce electricity from hydrogen).</t>
-  </si>
-  <si>
-    <t>Elasticity by Fuel (dimensionless)</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/analysis/studies/buildings/energyuse/pdf/price_elasticities.pdf</t>
-  </si>
-  <si>
-    <t>Price Elasticities for Energy Use in Buildings of the United States</t>
-  </si>
-  <si>
-    <t>We use same-price, long-run elasticities minus the 3-year short-run elasticities.</t>
-  </si>
-  <si>
-    <t>We calculate it this way because we assume that 3-year elasticities primarily reflect behavior</t>
-  </si>
-  <si>
-    <t>all timescales.  So, the portion of the long-run elasticitiy represented by the 3-year elasticity</t>
-  </si>
-  <si>
-    <t>This is a subset of Table 1 that includes only values from AEO2020 (not AEO99).</t>
-  </si>
-  <si>
-    <t>page 3: Table 1, Table 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Note from April 2023 - there has not been an updated version of this report. This is the most recent own-price elasticity data </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -488,9 +489,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -528,9 +529,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -563,26 +564,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -615,26 +599,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -809,17 +776,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="67.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -827,129 +794,129 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +931,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" customWidth="1"/>
@@ -975,19 +942,19 @@
     <col min="7" max="7" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1">
       <c r="A4" s="18" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -996,45 +963,45 @@
       <c r="F4" s="19"/>
       <c r="G4" s="19"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="12"/>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="13" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7">
         <v>-0.13</v>
@@ -1055,9 +1022,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="13" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7">
         <v>-0.08</v>
@@ -1078,9 +1045,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1">
       <c r="A9" s="14" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9">
         <v>-0.09</v>
@@ -1101,9 +1068,9 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1">
       <c r="A11" s="18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -1112,45 +1079,45 @@
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="12"/>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="6"/>
       <c r="E12" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="13" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7">
         <v>-0.08</v>
@@ -1171,9 +1138,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="13" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B15" s="7">
         <v>-0.03</v>
@@ -1194,9 +1161,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="15.75" thickBot="1">
       <c r="A16" s="14" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B16" s="9">
         <v>-0.13</v>
@@ -1217,9 +1184,9 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1234,30 +1201,30 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="30">
       <c r="A1" s="23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B2" s="22">
         <f>'EIA Table 1'!E7-'EIA Table 1'!D7</f>
@@ -1272,9 +1239,9 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B3" s="21">
         <f>B5</f>
@@ -1289,9 +1256,9 @@
         <v>-3.999999999999998E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B4" s="22">
         <f>'EIA Table 1'!F8-'EIA Table 1'!D8</f>
@@ -1306,9 +1273,9 @@
         <v>-3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B5" s="22">
         <f>'EIA Table 1'!G9-'EIA Table 1'!D9</f>
@@ -1323,9 +1290,9 @@
         <v>-3.999999999999998E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1338,9 +1305,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1352,9 +1319,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B8" s="21">
         <f>B5</f>
@@ -1369,9 +1336,9 @@
         <v>-3.999999999999998E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B9" s="21">
         <f>B5</f>
@@ -1386,9 +1353,9 @@
         <v>-3.999999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B10" s="21">
         <f>B4</f>
@@ -1403,9 +1370,9 @@
         <v>-3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B11" s="21">
         <f>B2</f>
@@ -1426,4 +1393,175 @@
     <ignoredError sqref="C3" formula="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B6E1054-99D9-493C-BA76-D3267FE3A8CE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{375AF59C-C7B7-4FB1-B7D7-C9DCCA582996}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCAD583B-038C-43DE-831D-23E0DB3B761E}"/>
 </file>